--- a/diseases/d236/2010-2014.xlsx
+++ b/diseases/d236/2010-2014.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21264,7 +21264,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21657,7 +21657,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23871,7 +23871,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27015,7 +27015,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">

--- a/diseases/d236/2010-2014.xlsx
+++ b/diseases/d236/2010-2014.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21264,7 +21264,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21657,7 +21657,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23871,7 +23871,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27015,7 +27015,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
